--- a/Plano - 01-09 - Articulos con venta en 30 dias sin Stock GDU - copia.xlsx
+++ b/Plano - 01-09 - Articulos con venta en 30 dias sin Stock GDU - copia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\fs-depo102\J\Usuarios\Lucas L\Grupo Disco\Productos CON venta 30d sin Stock\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4437179B-B2CE-4DE5-B1F7-25D007F3A785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE89D2CE-6D7B-4E4E-911D-E7ADF353304C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="932" firstSheet="2" activeTab="12" xr2:uid="{52CC4510-3E45-4F48-8CF8-8D416B08CD5C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="932" firstSheet="16" activeTab="28" xr2:uid="{52CC4510-3E45-4F48-8CF8-8D416B08CD5C}"/>
   </bookViews>
   <sheets>
     <sheet name="GENERICO" sheetId="7" state="hidden" r:id="rId1"/>
@@ -34414,7 +34414,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -34439,7 +34439,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -34489,7 +34489,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>1715</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -34514,7 +34514,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>1187</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -34614,7 +34614,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>1346</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
@@ -34639,7 +34639,7 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -34689,7 +34689,7 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>44</v>
+        <v>595</v>
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
@@ -34714,7 +34714,7 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
@@ -34739,7 +34739,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>4150</v>
+        <v>3737</v>
       </c>
     </row>
   </sheetData>
@@ -34849,7 +34849,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>1749</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -34874,7 +34874,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>274</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -34899,7 +34899,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>235</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -34924,7 +34924,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>4150</v>
+        <v>3737</v>
       </c>
     </row>
   </sheetData>
@@ -35033,7 +35033,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>1981</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -35058,7 +35058,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1984</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -35083,7 +35083,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -35108,7 +35108,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>6496</v>
+        <v>784</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -35267,7 +35267,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -35292,7 +35292,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>840</v>
+        <v>593</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -35317,7 +35317,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>6282</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -35342,7 +35342,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>1382</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -35367,7 +35367,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>3699</v>
+        <v>3382</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -35392,7 +35392,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>1187</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -35417,7 +35417,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>6220</v>
+        <v>5557</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -35442,7 +35442,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>1346</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -35467,7 +35467,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
@@ -35492,7 +35492,7 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -35517,7 +35517,7 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>2365</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
@@ -35542,7 +35542,7 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>5634</v>
+        <v>5287</v>
       </c>
     </row>
   </sheetData>
@@ -35676,7 +35676,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>730</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -35701,7 +35701,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -35726,7 +35726,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -35776,7 +35776,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>1182</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -35801,7 +35801,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>6260</v>
+        <v>12525</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -35826,7 +35826,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>70</v>
+        <v>-51</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -35851,7 +35851,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>2304</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -35876,7 +35876,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>6900</v>
+        <v>8247</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
@@ -35901,7 +35901,7 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>2473</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -36001,7 +36001,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>2121</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
@@ -36051,7 +36051,7 @@
         <v>0</v>
       </c>
       <c r="G39">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.25">
@@ -36076,7 +36076,7 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>138</v>
+        <v>229</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
@@ -36126,7 +36126,7 @@
         <v>1</v>
       </c>
       <c r="G45">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
@@ -36151,7 +36151,7 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>342</v>
+        <v>294</v>
       </c>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.25">
@@ -36176,7 +36176,7 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>4150</v>
+        <v>3737</v>
       </c>
     </row>
   </sheetData>
@@ -36260,7 +36260,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -36285,7 +36285,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -36310,7 +36310,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>6282</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -36335,7 +36335,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>2604</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -36360,7 +36360,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>950</v>
+        <v>826</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -36385,7 +36385,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>1382</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -36410,7 +36410,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>1187</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -36435,7 +36435,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>522</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -36460,7 +36460,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>19</v>
+        <v>-120</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -36485,7 +36485,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>122</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -36610,7 +36610,7 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>13203</v>
+        <v>11836</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
@@ -36685,7 +36685,7 @@
         <v>0</v>
       </c>
       <c r="G39">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.25">
@@ -36710,7 +36710,7 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>44</v>
+        <v>595</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
@@ -36735,7 +36735,7 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <v>4150</v>
+        <v>3737</v>
       </c>
     </row>
   </sheetData>
@@ -36869,7 +36869,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1323</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -36994,7 +36994,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -37019,7 +37019,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>2632</v>
+        <v>2882</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -37044,7 +37044,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>1872</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -37069,7 +37069,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>2365</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
@@ -37094,7 +37094,7 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>646</v>
+        <v>331</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -37119,7 +37119,7 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>4150</v>
+        <v>3737</v>
       </c>
     </row>
   </sheetData>
@@ -37228,7 +37228,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -37303,7 +37303,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>10509</v>
+        <v>11174</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -37353,7 +37353,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -37378,7 +37378,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -37403,7 +37403,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>7</v>
+        <v>453</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -37453,7 +37453,7 @@
         <v>1</v>
       </c>
       <c r="G25">
-        <v>8376</v>
+        <v>2074</v>
       </c>
     </row>
   </sheetData>
@@ -37687,7 +37687,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -37737,7 +37737,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>2251</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -37762,7 +37762,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>1187</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -37862,7 +37862,7 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>2121</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
@@ -37887,7 +37887,7 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>1346</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
@@ -37912,7 +37912,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
@@ -37937,7 +37937,7 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>4150</v>
+        <v>3737</v>
       </c>
     </row>
   </sheetData>
@@ -38046,7 +38046,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -38071,7 +38071,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -38096,7 +38096,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1040</v>
+        <v>752</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -38121,7 +38121,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>3699</v>
+        <v>3382</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -38146,7 +38146,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>1187</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -38246,7 +38246,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -38271,7 +38271,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>1485</v>
+        <v>5031</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
@@ -38296,7 +38296,7 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -38321,7 +38321,7 @@
         <v>2</v>
       </c>
       <c r="G29">
-        <v>46138</v>
+        <v>19680</v>
       </c>
     </row>
   </sheetData>
@@ -38454,7 +38454,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -38479,7 +38479,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>3667</v>
+        <v>3288</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -38504,7 +38504,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -38529,7 +38529,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -38579,7 +38579,7 @@
         <v>1</v>
       </c>
       <c r="G19">
-        <v>1933</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -38604,7 +38604,7 @@
         <v>4</v>
       </c>
       <c r="G21">
-        <v>3316</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -38629,7 +38629,7 @@
         <v>3</v>
       </c>
       <c r="G23">
-        <v>439</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -38704,7 +38704,7 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>3699</v>
+        <v>3382</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
@@ -38729,7 +38729,7 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>1187</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
@@ -38754,7 +38754,7 @@
         <v>2</v>
       </c>
       <c r="G33">
-        <v>20316</v>
+        <v>66666</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
@@ -38779,7 +38779,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>1321</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
@@ -38879,7 +38879,7 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <v>7545</v>
+        <v>7789</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
@@ -38954,7 +38954,7 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.25">
@@ -38979,7 +38979,7 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>352</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.25">
@@ -39004,7 +39004,7 @@
         <v>0</v>
       </c>
       <c r="G53">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
@@ -39029,7 +39029,7 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>2240</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
@@ -39054,7 +39054,7 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>1070</v>
+        <v>341</v>
       </c>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
@@ -39079,7 +39079,7 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>235</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.25">
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="G61">
-        <v>4150</v>
+        <v>3737</v>
       </c>
     </row>
   </sheetData>
@@ -39189,7 +39189,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -39314,7 +39314,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>275</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -39339,7 +39339,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>1323</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -39364,7 +39364,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>6260</v>
+        <v>12525</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -39389,7 +39389,7 @@
         <v>1</v>
       </c>
       <c r="G21">
-        <v>25864</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -39439,7 +39439,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>6900</v>
+        <v>8247</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
@@ -39514,7 +39514,7 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>7545</v>
+        <v>7789</v>
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
@@ -39539,7 +39539,7 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
@@ -39564,7 +39564,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>44</v>
+        <v>595</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
@@ -39589,7 +39589,7 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>2814</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
@@ -39614,7 +39614,7 @@
         <v>0</v>
       </c>
       <c r="G39">
-        <v>720</v>
+        <v>-92</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.25">
@@ -39639,7 +39639,7 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>4150</v>
+        <v>3737</v>
       </c>
     </row>
   </sheetData>
@@ -39773,7 +39773,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -39823,7 +39823,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>2814</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -39873,7 +39873,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>948</v>
+        <v>512</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -39898,7 +39898,7 @@
         <v>1</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>-267</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -39923,7 +39923,7 @@
         <v>1</v>
       </c>
       <c r="G21">
-        <v>1743</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -39948,7 +39948,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>34828</v>
+        <v>33544</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -39973,7 +39973,7 @@
         <v>4</v>
       </c>
       <c r="G25">
-        <v>9982</v>
+        <v>6116</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
@@ -39998,7 +39998,7 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>20166</v>
+        <v>17092</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -40023,7 +40023,7 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>25864</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
@@ -40048,7 +40048,7 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>6900</v>
+        <v>8247</v>
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
@@ -40073,7 +40073,7 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>6496</v>
+        <v>784</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
@@ -40098,7 +40098,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>2473</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
@@ -40123,7 +40123,7 @@
         <v>1</v>
       </c>
       <c r="G37">
-        <v>258</v>
+        <v>784</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
@@ -40173,7 +40173,7 @@
         <v>1</v>
       </c>
       <c r="G41">
-        <v>2592</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
@@ -40223,7 +40223,7 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>695</v>
+        <v>-120</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
@@ -40248,7 +40248,7 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>7545</v>
+        <v>7789</v>
       </c>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.25">
@@ -40273,7 +40273,7 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>1322</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.25">
@@ -40298,7 +40298,7 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>1394</v>
+        <v>979</v>
       </c>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.25">
@@ -40323,7 +40323,7 @@
         <v>0</v>
       </c>
       <c r="G53">
-        <v>1339</v>
+        <v>737</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
@@ -40348,7 +40348,7 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>134732</v>
+        <v>52710</v>
       </c>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
@@ -40373,7 +40373,7 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>260</v>
       </c>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
@@ -40448,7 +40448,7 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>46138</v>
+        <v>19680</v>
       </c>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.25">
@@ -40473,7 +40473,7 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>936</v>
+        <v>306</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.25">
@@ -40498,7 +40498,7 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>720</v>
+        <v>-92</v>
       </c>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.25">
@@ -40523,7 +40523,7 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>44970</v>
+        <v>10613</v>
       </c>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.25">
@@ -40548,7 +40548,7 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>264</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.25">
@@ -40573,7 +40573,7 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>726</v>
       </c>
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.25">
@@ -40598,7 +40598,7 @@
         <v>0</v>
       </c>
       <c r="G75">
-        <v>5634</v>
+        <v>5287</v>
       </c>
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.25">
@@ -40623,7 +40623,7 @@
         <v>0</v>
       </c>
       <c r="G77">
-        <v>4150</v>
+        <v>3737</v>
       </c>
     </row>
   </sheetData>
@@ -40732,7 +40732,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>1981</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -40757,7 +40757,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1376</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -40782,7 +40782,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>70</v>
+        <v>-51</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -40807,7 +40807,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>13471</v>
+        <v>11208</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -40832,7 +40832,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>1382</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -40857,7 +40857,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>7880</v>
+        <v>6440</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -40957,7 +40957,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
@@ -41007,7 +41007,7 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>4150</v>
+        <v>3737</v>
       </c>
     </row>
   </sheetData>
@@ -41141,7 +41141,7 @@
         <v>1</v>
       </c>
       <c r="G9">
-        <v>1093</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -41166,7 +41166,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>948</v>
+        <v>512</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -41191,7 +41191,7 @@
         <v>2</v>
       </c>
       <c r="G13">
-        <v>17756</v>
+        <v>14627</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -41216,7 +41216,7 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>4775</v>
+        <v>3918</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -41241,7 +41241,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>879</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -41266,7 +41266,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>1382</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -41291,7 +41291,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>7880</v>
+        <v>6440</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -41316,7 +41316,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>591</v>
+        <v>346</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -41366,7 +41366,7 @@
         <v>2</v>
       </c>
       <c r="G27">
-        <v>10509</v>
+        <v>11174</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -41391,7 +41391,7 @@
         <v>2</v>
       </c>
       <c r="G29">
-        <v>32970</v>
+        <v>26668</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
@@ -41416,7 +41416,7 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>1305</v>
+        <v>528</v>
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
@@ -41441,7 +41441,7 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>1346</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
@@ -41466,7 +41466,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>134732</v>
+        <v>52710</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
@@ -41491,7 +41491,7 @@
         <v>3</v>
       </c>
       <c r="G37">
-        <v>176114</v>
+        <v>211543</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
@@ -41516,7 +41516,7 @@
         <v>4</v>
       </c>
       <c r="G39">
-        <v>83401</v>
+        <v>215882</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.25">
@@ -41541,7 +41541,7 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
@@ -41566,7 +41566,7 @@
         <v>3</v>
       </c>
       <c r="G43">
-        <v>44970</v>
+        <v>10613</v>
       </c>
     </row>
   </sheetData>
@@ -41725,7 +41725,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -41750,7 +41750,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -41800,7 +41800,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>2674</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -41850,7 +41850,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>20316</v>
+        <v>66666</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -41875,7 +41875,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>19</v>
+        <v>-120</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -42000,7 +42000,7 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>7545</v>
+        <v>7789</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
@@ -42025,7 +42025,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>1346</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
@@ -42050,7 +42050,7 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
@@ -42100,7 +42100,7 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>2365</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
@@ -42125,7 +42125,7 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <v>4150</v>
+        <v>3737</v>
       </c>
     </row>
   </sheetData>
@@ -42234,7 +42234,7 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>1382</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -42284,7 +42284,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>660</v>
+        <v>643</v>
       </c>
     </row>
   </sheetData>
@@ -42393,7 +42393,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -42418,7 +42418,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1981</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -42468,7 +42468,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -42593,7 +42593,7 @@
         <v>1</v>
       </c>
       <c r="G23">
-        <v>3633</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -42718,7 +42718,7 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
@@ -42768,7 +42768,7 @@
         <v>1</v>
       </c>
       <c r="G37">
-        <v>14884</v>
+        <v>15586</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
@@ -42793,7 +42793,7 @@
         <v>0</v>
       </c>
       <c r="G39">
-        <v>720</v>
+        <v>-92</v>
       </c>
     </row>
   </sheetData>
@@ -42877,7 +42877,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -42902,7 +42902,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>3699</v>
+        <v>3382</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -43002,7 +43002,7 @@
         <v>3</v>
       </c>
       <c r="G15">
-        <v>4461</v>
+        <v>3389</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -43027,7 +43027,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -43052,7 +43052,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>12150</v>
+        <v>11237</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -43077,7 +43077,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>352</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -43102,7 +43102,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>176114</v>
+        <v>211543</v>
       </c>
     </row>
   </sheetData>
@@ -43236,7 +43236,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>8411</v>
+        <v>6945</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -43286,7 +43286,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>1312</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -43311,7 +43311,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>1892</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -43336,7 +43336,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>3313</v>
+        <v>2994</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -43361,7 +43361,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>4345</v>
+        <v>3772</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -43386,7 +43386,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>3403</v>
+        <v>15226</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -43411,7 +43411,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>1841</v>
+        <v>3816</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -43436,7 +43436,7 @@
         <v>1</v>
       </c>
       <c r="G25">
-        <v>1182</v>
+        <v>263</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
@@ -43461,7 +43461,7 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>-267</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -43486,7 +43486,7 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>5373</v>
+        <v>16127</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
@@ -43511,7 +43511,7 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>1743</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
@@ -43536,7 +43536,7 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>225</v>
+        <v>160</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
@@ -43586,7 +43586,7 @@
         <v>1</v>
       </c>
       <c r="G37">
-        <v>6496</v>
+        <v>784</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
@@ -43636,7 +43636,7 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>6849</v>
+        <v>9093</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
@@ -43661,7 +43661,7 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <v>32970</v>
+        <v>26668</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
@@ -43686,7 +43686,7 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>864</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
@@ -43711,7 +43711,7 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.25">
@@ -43736,7 +43736,7 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>2781</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.25">
@@ -43761,7 +43761,7 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>936</v>
+        <v>306</v>
       </c>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.25">
@@ -43786,7 +43786,7 @@
         <v>0</v>
       </c>
       <c r="G53">
-        <v>646</v>
+        <v>331</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
@@ -43811,7 +43811,7 @@
         <v>1</v>
       </c>
       <c r="G55">
-        <v>53695</v>
+        <v>15866</v>
       </c>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
@@ -43836,7 +43836,7 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>8809</v>
+        <v>6401</v>
       </c>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
@@ -43861,7 +43861,7 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>8376</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.25">
@@ -43886,7 +43886,7 @@
         <v>0</v>
       </c>
       <c r="G61">
-        <v>9168</v>
+        <v>3852</v>
       </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.25">
@@ -43911,7 +43911,7 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.25">
@@ -43936,7 +43936,7 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>4150</v>
+        <v>3737</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.25">
@@ -43961,7 +43961,7 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>660</v>
+        <v>643</v>
       </c>
     </row>
   </sheetData>
@@ -44145,7 +44145,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>663</v>
+        <v>559</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -44170,7 +44170,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>10195</v>
+        <v>8313</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -44245,7 +44245,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>666</v>
+        <v>566</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -44270,7 +44270,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -44320,7 +44320,7 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>1984</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -44345,7 +44345,7 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>3500</v>
+        <v>3394</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
@@ -44370,7 +44370,7 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>2461</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
@@ -44395,7 +44395,7 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>3699</v>
+        <v>3382</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
@@ -44420,7 +44420,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>1187</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
@@ -44445,7 +44445,7 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>275</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
@@ -44595,7 +44595,7 @@
         <v>1</v>
       </c>
       <c r="G49">
-        <v>32970</v>
+        <v>26668</v>
       </c>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.25">
@@ -44620,7 +44620,7 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>6220</v>
+        <v>5557</v>
       </c>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.25">
@@ -44645,7 +44645,7 @@
         <v>0</v>
       </c>
       <c r="G53">
-        <v>11496</v>
+        <v>7699</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
@@ -44695,7 +44695,7 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>5232</v>
+        <v>5026</v>
       </c>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
@@ -44720,7 +44720,7 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>4150</v>
+        <v>3737</v>
       </c>
     </row>
   </sheetData>
@@ -44828,7 +44828,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -44853,7 +44853,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>460</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -44878,7 +44878,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -44903,7 +44903,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -44928,7 +44928,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -44978,7 +44978,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>70</v>
+        <v>-51</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -45003,7 +45003,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>275</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -45028,7 +45028,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>23</v>
+        <v>5783</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -45103,7 +45103,7 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>399</v>
+        <v>279</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
@@ -45128,7 +45128,7 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>745</v>
+        <v>428</v>
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
@@ -45178,7 +45178,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
@@ -45203,7 +45203,7 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>2240</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
@@ -45228,7 +45228,7 @@
         <v>0</v>
       </c>
       <c r="G39">
-        <v>1491</v>
+        <v>1016</v>
       </c>
     </row>
   </sheetData>
@@ -45313,7 +45313,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -45363,7 +45363,7 @@
         <v>3</v>
       </c>
       <c r="G9">
-        <v>5750</v>
+        <v>8165</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -45463,7 +45463,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>344</v>
+        <v>-151</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -45488,7 +45488,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -45513,7 +45513,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>1612</v>
+        <v>924</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -45538,7 +45538,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>297</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>
@@ -45672,7 +45672,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1436</v>
+        <v>599</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -45697,7 +45697,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>19982</v>
+        <v>19313</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -45722,7 +45722,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -45747,7 +45747,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -45797,7 +45797,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>539</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -45822,7 +45822,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>1410</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -45847,7 +45847,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>-267</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -45872,7 +45872,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>275</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
@@ -45897,7 +45897,7 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>3633</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -45922,7 +45922,7 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>6496</v>
+        <v>784</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
@@ -45947,7 +45947,7 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>258</v>
+        <v>784</v>
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
@@ -45997,7 +45997,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>3118</v>
+        <v>2865</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
@@ -46022,7 +46022,7 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>7545</v>
+        <v>7789</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
@@ -46047,7 +46047,7 @@
         <v>0</v>
       </c>
       <c r="G39">
-        <v>1079</v>
+        <v>233</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.25">
@@ -46072,7 +46072,7 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
@@ -46097,7 +46097,7 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <v>2748</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
@@ -46122,7 +46122,7 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>2146</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
@@ -46147,7 +46147,7 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.25">
@@ -46172,7 +46172,7 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>2195</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.25">
@@ -46197,7 +46197,7 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>601</v>
+        <v>391</v>
       </c>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.25">
@@ -46222,7 +46222,7 @@
         <v>0</v>
       </c>
       <c r="G53">
-        <v>1225</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
@@ -46247,7 +46247,7 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>4150</v>
+        <v>3737</v>
       </c>
     </row>
   </sheetData>
@@ -46331,7 +46331,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -46381,7 +46381,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1410</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -46406,7 +46406,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1323</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -46481,7 +46481,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -46556,7 +46556,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>2814</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -46581,7 +46581,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>2365</v>
+        <v>1551</v>
       </c>
     </row>
   </sheetData>
@@ -46666,7 +46666,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -46691,7 +46691,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>45991</v>
+        <v>43119</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -46716,7 +46716,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -46741,7 +46741,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>840</v>
+        <v>593</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -46766,7 +46766,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>948</v>
+        <v>512</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -46816,7 +46816,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>617</v>
+        <v>545</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -46841,7 +46841,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>2304</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -46916,7 +46916,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>2473</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
@@ -46941,7 +46941,7 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>20316</v>
+        <v>66666</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -47016,7 +47016,7 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>13203</v>
+        <v>11836</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
@@ -47041,7 +47041,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>6220</v>
+        <v>5557</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
@@ -47066,7 +47066,7 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>344</v>
+        <v>-151</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
@@ -47091,7 +47091,7 @@
         <v>0</v>
       </c>
       <c r="G39">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.25">
@@ -47116,7 +47116,7 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>10042</v>
+        <v>6703</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
@@ -47166,7 +47166,7 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>1612</v>
+        <v>924</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
@@ -47191,7 +47191,7 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>5803</v>
+        <v>4417</v>
       </c>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.25">
@@ -47216,7 +47216,7 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>46138</v>
+        <v>19680</v>
       </c>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.25">
@@ -47241,7 +47241,7 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>12611</v>
+        <v>10258</v>
       </c>
     </row>
   </sheetData>
@@ -48853,7 +48853,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -48878,7 +48878,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -48903,7 +48903,7 @@
         <v>1</v>
       </c>
       <c r="G9">
-        <v>1970</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -48928,7 +48928,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -48953,7 +48953,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -49003,7 +49003,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>823</v>
+        <v>706</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -49028,7 +49028,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>-267</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -49053,7 +49053,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>429</v>
+        <v>389</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -49078,7 +49078,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>70</v>
+        <v>-51</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -49128,7 +49128,7 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>32970</v>
+        <v>26668</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -49178,7 +49178,7 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>2121</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
@@ -49228,7 +49228,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
@@ -49253,7 +49253,7 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>176114</v>
+        <v>211543</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
@@ -49278,7 +49278,7 @@
         <v>0</v>
       </c>
       <c r="G39">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.25">
@@ -49303,7 +49303,7 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>274</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
@@ -49328,7 +49328,7 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <v>129</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
@@ -49353,7 +49353,7 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
@@ -49378,7 +49378,7 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>936</v>
+        <v>306</v>
       </c>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.25">
@@ -49403,7 +49403,7 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>264</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.25">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>12182</v>
+        <v>5544</v>
       </c>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.25">
@@ -49478,7 +49478,7 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
@@ -49503,7 +49503,7 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>1225</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
@@ -49528,7 +49528,7 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>4150</v>
+        <v>3737</v>
       </c>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.25">
@@ -49553,7 +49553,7 @@
         <v>0</v>
       </c>
       <c r="G61">
-        <v>13027</v>
+        <v>12241</v>
       </c>
     </row>
   </sheetData>
@@ -52528,7 +52528,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -52578,7 +52578,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -52603,7 +52603,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>275</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -52678,7 +52678,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -52703,7 +52703,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>3462</v>
+        <v>6243</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
@@ -52728,7 +52728,7 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>720</v>
+        <v>-92</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -52753,7 +52753,7 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>4150</v>
+        <v>3737</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -55360,7 +55360,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -55435,7 +55435,7 @@
         <v>6</v>
       </c>
       <c r="G11">
-        <v>40896</v>
+        <v>38955</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -55485,7 +55485,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>70</v>
+        <v>-51</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -55510,7 +55510,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>11</v>
+        <v>299</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -55535,7 +55535,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>3699</v>
+        <v>3382</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -55585,7 +55585,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>19</v>
+        <v>-120</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -55610,7 +55610,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>1321</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
@@ -55785,7 +55785,7 @@
         <v>0</v>
       </c>
       <c r="G39">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.25">
@@ -55810,7 +55810,7 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>1207</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
@@ -55835,7 +55835,7 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <v>1491</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
@@ -55860,7 +55860,7 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>4150</v>
+        <v>3737</v>
       </c>
     </row>
   </sheetData>
@@ -58084,7 +58084,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -58134,7 +58134,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1187</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -58209,7 +58209,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -58234,7 +58234,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>4150</v>
+        <v>3737</v>
       </c>
     </row>
   </sheetData>
@@ -60384,7 +60384,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -60409,7 +60409,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>6282</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -60434,7 +60434,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>2872</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -60459,7 +60459,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>70</v>
+        <v>-51</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -60484,7 +60484,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>1382</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -60509,7 +60509,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>2022</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -60584,7 +60584,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>2121</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -60634,7 +60634,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>1346</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
@@ -60659,7 +60659,7 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -60684,7 +60684,7 @@
         <v>1</v>
       </c>
       <c r="G29">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
@@ -60709,7 +60709,7 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>4150</v>
+        <v>3737</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -75497,7 +75497,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="5">
-        <v>1187</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -75622,7 +75622,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -75647,7 +75647,7 @@
         <v>1</v>
       </c>
       <c r="G19" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -75672,7 +75672,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="5">
-        <v>274</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -75697,7 +75697,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="5">
-        <v>129</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -75722,7 +75722,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="5">
-        <v>4150</v>
+        <v>3737</v>
       </c>
     </row>
   </sheetData>
